--- a/analysis/econometrics_outputs/contdid/Graficos/contracts/dose/contdid_cosine_weighted_dose_att.xlsx
+++ b/analysis/econometrics_outputs/contdid/Graficos/contracts/dose/contdid_cosine_weighted_dose_att.xlsx
@@ -488,10 +488,10 @@
         <v>182.950453767006</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>1099.92076701915</v>
+        <v>655.009173851175</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
@@ -510,10 +510,10 @@
         <v>181.069478308898</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>1019.38912406201</v>
+        <v>623.176214141416</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
@@ -532,10 +532,10 @@
         <v>179.790528827343</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>962.664419539976</v>
+        <v>582.721881496525</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
@@ -554,10 +554,10 @@
         <v>178.68450782873</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>912.074191849626</v>
+        <v>552.277217458097</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
@@ -576,10 +576,10 @@
         <v>177.259498532065</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>844.373322718647</v>
+        <v>520.845294735344</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
@@ -598,10 +598,10 @@
         <v>175.899194318684</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>776.469217394949</v>
+        <v>469.095372959712</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -620,10 +620,10 @@
         <v>175.403771476425</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>750.766763282129</v>
+        <v>449.637802160803</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -642,10 +642,10 @@
         <v>174.804242360491</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>718.840886773938</v>
+        <v>443.256268871096</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -664,10 +664,10 @@
         <v>174.072461439145</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>678.462084631621</v>
+        <v>436.878594952708</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
@@ -686,10 +686,10 @@
         <v>173.480971089938</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>644.484674143055</v>
+        <v>421.19495262546</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
@@ -708,10 +708,10 @@
         <v>172.738672971117</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>599.766162605771</v>
+        <v>419.815927015652</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
@@ -730,10 +730,10 @@
         <v>172.035531636944</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>554.710571829643</v>
+        <v>406.78594521619</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
@@ -752,10 +752,10 @@
         <v>169.99950842567</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>397.801918469865</v>
+        <v>330.950118753742</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
@@ -774,10 +774,10 @@
         <v>169.351533404552</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>328.821708769868</v>
+        <v>331.475969543871</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
@@ -796,10 +796,10 @@
         <v>168.958210280866</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>317.35247919006</v>
+        <v>342.395687232337</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
@@ -818,10 +818,10 @@
         <v>168.6625277115</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>309.953853828932</v>
+        <v>340.492907534283</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
@@ -840,10 +840,10 @@
         <v>168.806938156858</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>231.656568526753</v>
+        <v>368.989474912185</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
@@ -862,10 +862,10 @@
         <v>168.999947437839</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>194.600275063211</v>
+        <v>368.26076954702</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
@@ -884,10 +884,10 @@
         <v>169.480719647272</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>137.99625977929</v>
+        <v>389.98316692061</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
@@ -906,10 +906,10 @@
         <v>169.984958802515</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>102.495089344162</v>
+        <v>388.932717664018</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
@@ -928,10 +928,10 @@
         <v>170.558026773951</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>96.1091704173106</v>
+        <v>393.056746056742</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
@@ -950,10 +950,10 @@
         <v>170.9957182655</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>91.9134125048492</v>
+        <v>390.623113400008</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
@@ -972,10 +972,10 @@
         <v>172.9238046149</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>62.1914597487212</v>
+        <v>411.895113205502</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
@@ -994,10 +994,10 @@
         <v>174.462931329543</v>
       </c>
       <c r="F29" s="1" t="n">
-        <v>72.0480052040016</v>
+        <v>432.127936954178</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
@@ -1016,10 +1016,10 @@
         <v>176.265495422021</v>
       </c>
       <c r="F30" s="1" t="n">
-        <v>108.358174161716</v>
+        <v>429.341033805602</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
@@ -1038,10 +1038,10 @@
         <v>176.719221762843</v>
       </c>
       <c r="F31" s="1" t="n">
-        <v>116.132930585525</v>
+        <v>426.118774747421</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
@@ -1060,10 +1060,10 @@
         <v>177.80759727455</v>
       </c>
       <c r="F32" s="1" t="n">
-        <v>132.998048951921</v>
+        <v>412.436212918884</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
@@ -1082,10 +1082,10 @@
         <v>178.181454197605</v>
       </c>
       <c r="F33" s="1" t="n">
-        <v>138.272493083338</v>
+        <v>409.709527301163</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
@@ -1104,10 +1104,10 @@
         <v>180.346613080997</v>
       </c>
       <c r="F34" s="1" t="n">
-        <v>164.510045217509</v>
+        <v>409.401648054019</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
@@ -1126,10 +1126,10 @@
         <v>181.179650277358</v>
       </c>
       <c r="F35" s="1" t="n">
-        <v>172.938487010577</v>
+        <v>408.223842708838</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
@@ -1148,10 +1148,10 @@
         <v>183.093462837745</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>189.465855896544</v>
+        <v>407.055291214352</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
@@ -1170,10 +1170,10 @@
         <v>184.197022062146</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>197.446471259457</v>
+        <v>401.675333718724</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
@@ -1192,10 +1192,10 @@
         <v>187.928193297657</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>217.748442559458</v>
+        <v>394.273513304529</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
@@ -1214,10 +1214,10 @@
         <v>191.525049844824</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>229.71402219365</v>
+        <v>376.229978755804</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
@@ -1236,10 +1236,10 @@
         <v>193.701528231756</v>
       </c>
       <c r="F40" s="1" t="n">
-        <v>234.159141478666</v>
+        <v>370.177219142931</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
@@ -1258,10 +1258,10 @@
         <v>198.428605972979</v>
       </c>
       <c r="F41" s="1" t="n">
-        <v>231.930557275842</v>
+        <v>346.438140695195</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
@@ -1280,10 +1280,10 @@
         <v>202.285086699461</v>
       </c>
       <c r="F42" s="1" t="n">
-        <v>222.773222976247</v>
+        <v>334.382944027163</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
@@ -1302,10 +1302,10 @@
         <v>205.210527572137</v>
       </c>
       <c r="F43" s="1" t="n">
-        <v>214.052659209307</v>
+        <v>320.101598633569</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
@@ -1324,10 +1324,10 @@
         <v>206.565291203044</v>
       </c>
       <c r="F44" s="1" t="n">
-        <v>209.589007300293</v>
+        <v>315.885628175756</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
@@ -1346,10 +1346,10 @@
         <v>213.5793207266</v>
       </c>
       <c r="F45" s="1" t="n">
-        <v>183.350722121322</v>
+        <v>284.89607267059</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
@@ -1368,10 +1368,10 @@
         <v>216.724552560832</v>
       </c>
       <c r="F46" s="1" t="n">
-        <v>170.528009972884</v>
+        <v>271.825149502536</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
@@ -1390,10 +1390,10 @@
         <v>223.283750703014</v>
       </c>
       <c r="F47" s="1" t="n">
-        <v>143.159057387013</v>
+        <v>227.861593670014</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H47" s="1"/>
       <c r="I47" s="1"/>
@@ -1412,10 +1412,10 @@
         <v>227.847152078539</v>
       </c>
       <c r="F48" s="1" t="n">
-        <v>123.695993210543</v>
+        <v>201.598344019624</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H48" s="1"/>
       <c r="I48" s="1"/>
@@ -1434,10 +1434,10 @@
         <v>229.146035114678</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>114.974277903421</v>
+        <v>196.884945040569</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H49" s="1"/>
       <c r="I49" s="1"/>
@@ -1456,10 +1456,10 @@
         <v>231.861301470593</v>
       </c>
       <c r="F50" s="1" t="n">
-        <v>104.578249775242</v>
+        <v>184.850469606616</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
@@ -1478,10 +1478,10 @@
         <v>240.399013331839</v>
       </c>
       <c r="F51" s="1" t="n">
-        <v>78.5935203271835</v>
+        <v>145.162421971166</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H51" s="1"/>
       <c r="I51" s="1"/>
@@ -1500,10 +1500,10 @@
         <v>245.876494492717</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>89.4477523943153</v>
+        <v>139.971637859566</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H52" s="1"/>
       <c r="I52" s="1"/>
@@ -1522,10 +1522,10 @@
         <v>247.777039900903</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>99.8739981963303</v>
+        <v>142.57137924938</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
@@ -1544,10 +1544,10 @@
         <v>249.040405034703</v>
       </c>
       <c r="F54" s="1" t="n">
-        <v>106.63179535738</v>
+        <v>137.24390581014</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
@@ -1566,10 +1566,10 @@
         <v>249.590279775806</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>107.818138783278</v>
+        <v>134.897923533024</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H55" s="1"/>
       <c r="I55" s="1"/>
@@ -1588,10 +1588,10 @@
         <v>257.428386269211</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>112.57780836665</v>
+        <v>143.770606049883</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
@@ -1610,10 +1610,10 @@
         <v>264.883616890371</v>
       </c>
       <c r="F57" s="1" t="n">
-        <v>130.517517743602</v>
+        <v>146.103586940031</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H57" s="1"/>
       <c r="I57" s="1"/>
@@ -1632,10 +1632,10 @@
         <v>266.204371445166</v>
       </c>
       <c r="F58" s="1" t="n">
-        <v>133.143383576901</v>
+        <v>149.728334875439</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H58" s="1"/>
       <c r="I58" s="1"/>
@@ -1654,10 +1654,10 @@
         <v>270.304585293548</v>
       </c>
       <c r="F59" s="1" t="n">
-        <v>138.790854153998</v>
+        <v>159.785609367139</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H59" s="1"/>
       <c r="I59" s="1"/>
@@ -1676,10 +1676,10 @@
         <v>272.915361271888</v>
       </c>
       <c r="F60" s="1" t="n">
-        <v>136.751355759902</v>
+        <v>165.964824759093</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
@@ -1698,10 +1698,10 @@
         <v>273.14546606271</v>
       </c>
       <c r="F61" s="1" t="n">
-        <v>136.518214802528</v>
+        <v>165.26256456388</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
@@ -1720,10 +1720,10 @@
         <v>273.14546606271</v>
       </c>
       <c r="F62" s="1" t="n">
-        <v>136.518214802528</v>
+        <v>165.26256456388</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H62" s="1"/>
       <c r="I62" s="1"/>
@@ -1742,10 +1742,10 @@
         <v>274.288004319276</v>
       </c>
       <c r="F63" s="1" t="n">
-        <v>135.263372127814</v>
+        <v>162.492409978155</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H63" s="1"/>
       <c r="I63" s="1"/>
@@ -1764,10 +1764,10 @@
         <v>274.723221385206</v>
       </c>
       <c r="F64" s="1" t="n">
-        <v>134.743523085067</v>
+        <v>162.69977676253</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H64" s="1"/>
       <c r="I64" s="1"/>
@@ -1786,10 +1786,10 @@
         <v>276.918248501426</v>
       </c>
       <c r="F65" s="1" t="n">
-        <v>131.793966446176</v>
+        <v>162.215116090465</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H65" s="1"/>
       <c r="I65" s="1"/>
@@ -1808,10 +1808,10 @@
         <v>277.281379051569</v>
       </c>
       <c r="F66" s="1" t="n">
-        <v>131.257942053672</v>
+        <v>161.002113098194</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H66" s="1"/>
       <c r="I66" s="1"/>
@@ -1830,10 +1830,10 @@
         <v>281.602034441691</v>
       </c>
       <c r="F67" s="1" t="n">
-        <v>124.177487899229</v>
+        <v>151.853310888531</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H67" s="1"/>
       <c r="I67" s="1"/>
@@ -1852,10 +1852,10 @@
         <v>282.356485918737</v>
       </c>
       <c r="F68" s="1" t="n">
-        <v>122.868808328798</v>
+        <v>150.657909871976</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H68" s="1"/>
       <c r="I68" s="1"/>
@@ -1874,10 +1874,10 @@
         <v>284.888290300937</v>
       </c>
       <c r="F69" s="1" t="n">
-        <v>118.494059485553</v>
+        <v>145.904247190959</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H69" s="1"/>
       <c r="I69" s="1"/>
@@ -1896,10 +1896,10 @@
         <v>287.380858852758</v>
       </c>
       <c r="F70" s="1" t="n">
-        <v>111.90023778681</v>
+        <v>135.756144393185</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H70" s="1"/>
       <c r="I70" s="1"/>
@@ -1918,10 +1918,10 @@
         <v>291.205343238295</v>
       </c>
       <c r="F71" s="1" t="n">
-        <v>100.835036554466</v>
+        <v>131.977979741861</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H71" s="1"/>
       <c r="I71" s="1"/>
@@ -1940,10 +1940,10 @@
         <v>294.384375037847</v>
       </c>
       <c r="F72" s="1" t="n">
-        <v>92.1919319722257</v>
+        <v>135.971178118234</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H72" s="1"/>
       <c r="I72" s="1"/>
@@ -1962,10 +1962,10 @@
         <v>298.32048735243</v>
       </c>
       <c r="F73" s="1" t="n">
-        <v>82.4437252940258</v>
+        <v>128.82298511485</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H73" s="1"/>
       <c r="I73" s="1"/>
@@ -1984,10 +1984,10 @@
         <v>306.437944225718</v>
       </c>
       <c r="F74" s="1" t="n">
-        <v>65.7336218718903</v>
+        <v>116.334598894742</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H74" s="1"/>
       <c r="I74" s="1"/>
@@ -2006,10 +2006,10 @@
         <v>313.770862740829</v>
       </c>
       <c r="F75" s="1" t="n">
-        <v>60.5891077240226</v>
+        <v>134.071541192306</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H75" s="1"/>
       <c r="I75" s="1"/>
@@ -2028,10 +2028,10 @@
         <v>326.901755454256</v>
       </c>
       <c r="F76" s="1" t="n">
-        <v>66.0436341089577</v>
+        <v>140.113682106787</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H76" s="1"/>
       <c r="I76" s="1"/>
@@ -2050,10 +2050,10 @@
         <v>336.111626718154</v>
       </c>
       <c r="F77" s="1" t="n">
-        <v>69.7045897796482</v>
+        <v>154.321804534902</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H77" s="1"/>
       <c r="I77" s="1"/>
@@ -2072,10 +2072,10 @@
         <v>348.548683298364</v>
       </c>
       <c r="F78" s="1" t="n">
-        <v>74.315798889855</v>
+        <v>175.072472355134</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H78" s="1"/>
       <c r="I78" s="1"/>
@@ -2094,10 +2094,10 @@
         <v>355.553195661636</v>
       </c>
       <c r="F79" s="1" t="n">
-        <v>76.7356326374694</v>
+        <v>180.833664772943</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H79" s="1"/>
       <c r="I79" s="1"/>
@@ -2116,10 +2116,10 @@
         <v>361.239835333364</v>
       </c>
       <c r="F80" s="1" t="n">
-        <v>76.1707689594489</v>
+        <v>186.697730771975</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H80" s="1"/>
       <c r="I80" s="1"/>
@@ -2138,10 +2138,10 @@
         <v>366.932858997709</v>
       </c>
       <c r="F81" s="1" t="n">
-        <v>70.2133217095196</v>
+        <v>192.673261817673</v>
       </c>
       <c r="G81" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H81" s="1"/>
       <c r="I81" s="1"/>
@@ -2160,10 +2160,10 @@
         <v>374.228128402807</v>
       </c>
       <c r="F82" s="1" t="n">
-        <v>62.75074335884</v>
+        <v>199.833405855676</v>
       </c>
       <c r="G82" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H82" s="1"/>
       <c r="I82" s="1"/>
@@ -2182,10 +2182,10 @@
         <v>380.796043595585</v>
       </c>
       <c r="F83" s="1" t="n">
-        <v>57.2920271733177</v>
+        <v>197.309679511463</v>
       </c>
       <c r="G83" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H83" s="1"/>
       <c r="I83" s="1"/>
@@ -2204,10 +2204,10 @@
         <v>391.398095181458</v>
       </c>
       <c r="F84" s="1" t="n">
-        <v>57.0823960286129</v>
+        <v>206.827190160727</v>
       </c>
       <c r="G84" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H84" s="1"/>
       <c r="I84" s="1"/>
@@ -2226,10 +2226,10 @@
         <v>440.256419477869</v>
       </c>
       <c r="F85" s="1" t="n">
-        <v>40.0228261013511</v>
+        <v>218.802785840705</v>
       </c>
       <c r="G85" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H85" s="1"/>
       <c r="I85" s="1"/>
@@ -2248,10 +2248,10 @@
         <v>453.782697828872</v>
       </c>
       <c r="F86" s="1" t="n">
-        <v>40.6576179699091</v>
+        <v>222.14910473783</v>
       </c>
       <c r="G86" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H86" s="1"/>
       <c r="I86" s="1"/>
@@ -2270,10 +2270,10 @@
         <v>532.710740991239</v>
       </c>
       <c r="F87" s="1" t="n">
-        <v>60.9922249289723</v>
+        <v>245.556508602255</v>
       </c>
       <c r="G87" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H87" s="1"/>
       <c r="I87" s="1"/>
@@ -2292,10 +2292,10 @@
         <v>587.609105481563</v>
       </c>
       <c r="F88" s="1" t="n">
-        <v>104.428126816391</v>
+        <v>225.941332781983</v>
       </c>
       <c r="G88" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H88" s="1"/>
       <c r="I88" s="1"/>
@@ -2314,10 +2314,10 @@
         <v>592.767880774047</v>
       </c>
       <c r="F89" s="1" t="n">
-        <v>108.851248995114</v>
+        <v>224.269428937279</v>
       </c>
       <c r="G89" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H89" s="1"/>
       <c r="I89" s="1"/>
@@ -2336,10 +2336,10 @@
         <v>645.979696810038</v>
       </c>
       <c r="F90" s="1" t="n">
-        <v>141.844587808525</v>
+        <v>233.749479645172</v>
       </c>
       <c r="G90" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H90" s="1"/>
       <c r="I90" s="1"/>
@@ -2358,10 +2358,10 @@
         <v>709.442867072301</v>
       </c>
       <c r="F91" s="1" t="n">
-        <v>194.126945660561</v>
+        <v>259.524050171844</v>
       </c>
       <c r="G91" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H91" s="1"/>
       <c r="I91" s="1"/>
@@ -2380,10 +2380,10 @@
         <v>807.823805756917</v>
       </c>
       <c r="F92" s="1" t="n">
-        <v>283.968492131193</v>
+        <v>293.067741810367</v>
       </c>
       <c r="G92" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H92" s="1"/>
       <c r="I92" s="1"/>
@@ -2402,10 +2402,10 @@
         <v>812.096130833123</v>
       </c>
       <c r="F93" s="1" t="n">
-        <v>288.054904337783</v>
+        <v>292.170387798802</v>
       </c>
       <c r="G93" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H93" s="1"/>
       <c r="I93" s="1"/>
@@ -2424,10 +2424,10 @@
         <v>988.77587104382</v>
       </c>
       <c r="F94" s="1" t="n">
-        <v>467.708975909311</v>
+        <v>385.526327569536</v>
       </c>
       <c r="G94" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H94" s="1"/>
       <c r="I94" s="1"/>
@@ -2446,10 +2446,10 @@
         <v>1206.99637070733</v>
       </c>
       <c r="F95" s="1" t="n">
-        <v>711.553016409842</v>
+        <v>546.346336889093</v>
       </c>
       <c r="G95" s="1" t="n">
-        <v>6.28498389737027</v>
+        <v>2.30349423833549</v>
       </c>
       <c r="H95" s="1"/>
       <c r="I95" s="1"/>
